--- a/VerveStacks_MYS_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_MYS_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MYS_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98F284D7-B2A1-4BF6-91AA-9EE1973C08EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54A1723B-29AF-46D7-95CB-FECC9B302A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -663,7 +663,7 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S01aH02</t>
+    <t>S01aH02,S02aH02</t>
   </si>
   <si>
     <t>N</t>
@@ -711,19 +711,19 @@
     <t>S02aH06</t>
   </si>
   <si>
-    <t>S02aH02,S01aH02,S02aH04,S01aH03,S02aH03,S01aH04</t>
+    <t>S02aH04,S01aH03,S01aH02,S01aH04,S02aH03,S02aH02</t>
   </si>
   <si>
-    <t>S02aH05,S02aH01,S01aH05,S02aH06,S01aH01,S01aH06</t>
+    <t>S02aH06,S02aH05,S01aH06,S02aH01,S01aH05,S01aH01</t>
   </si>
   <si>
     <t>ts_036</t>
   </si>
   <si>
-    <t>S01aH03,S01aH02,S02aH03,S01aH04,S02aH04,S02aH02</t>
+    <t>S01aH02,S01aH04,S01aH03,S02aH02,S02aH04,S02aH03</t>
   </si>
   <si>
-    <t>S01aH05,S02aH05,S02aH01,S01aH01,S01aH06,S02aH06</t>
+    <t>S01aH05,S01aH06,S02aH05,S02aH06,S01aH01,S02aH01</t>
   </si>
   <si>
     <t>H07</t>
@@ -744,10 +744,10 @@
     <t>S02aH08</t>
   </si>
   <si>
-    <t>S02aH06,S01aH04,S02aH04,S02aH05,S01aH03,S01aH02,S02aH02,S01aH05,S01aH06,S02aH03</t>
+    <t>S02aH02,S01aH04,S02aH06,S01aH05,S02aH04,S02aH05,S01aH03,S01aH02,S01aH06,S02aH03</t>
   </si>
   <si>
-    <t>S01aH08,S02aH08,S01aH07,S02aH07,S02aH01,S01aH01</t>
+    <t>S02aH01,S01aH07,S02aH07,S01aH08,S02aH08,S01aH01</t>
   </si>
   <si>
     <t>AllS</t>
@@ -813,10 +813,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,RaD,RaP,FaP,SaP,WaD,FaD,WaP</t>
+    <t>WaP,FaP,SaP,FaD,SaD,WaD,RaD,RaP</t>
   </si>
   <si>
-    <t>WaP,SaN,WaN,FaP,SaP,FaN,RaP,RaN</t>
+    <t>SaN,WaN,FaN,RaN,RaP,WaP,FaP,SaP</t>
   </si>
 </sst>
 </file>
@@ -8436,7 +8436,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1880D85-576B-4684-9028-F2921821209F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5758BA13-DC45-454D-9EA0-9A70BC108B32}">
   <dimension ref="A9:AN27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9066,7 +9066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04340EE6-A817-4572-8414-91C031F89863}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{352A6435-B735-4013-9369-9AF08D7B7BAC}">
   <dimension ref="A9:AN214"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30345,7 +30345,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9327AB7-1A98-49C7-9BDF-410C6F14A014}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{968C4254-8E2B-4328-8F67-450A5DB266C5}">
   <dimension ref="A9:AN112"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33335,7 +33335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25392B99-7281-4EB4-B054-7C5B7BF832C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD68496C-6401-49DA-847A-0AA987C34E61}">
   <dimension ref="A9:AN214"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39157,7 +39157,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B844DD9-1BCF-47E5-9358-BAFD31632605}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E65F2833-BBEF-4B0A-A981-262C7EFF215B}">
   <dimension ref="A9:AN214"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44979,7 +44979,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80CC0D34-E2F9-4ECE-BE74-ED44C5A99947}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B04CFFAD-3274-470D-8157-5D6DF32E4D97}">
   <dimension ref="A9:AN282"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
